--- a/services/transactions/MASTER/HOTEL_TRANSACCIONES_MASTER.xlsx
+++ b/services/transactions/MASTER/HOTEL_TRANSACCIONES_MASTER.xlsx
@@ -2762,7 +2762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-11T18:28:48+00:00. Normalization version: v1.0.</t>
+          <t>Built 2026-05-11T19:19:17+00:00. Normalization version: v1.0.</t>
         </is>
       </c>
     </row>

--- a/services/transactions/MASTER/HOTEL_TRANSACCIONES_MASTER.xlsx
+++ b/services/transactions/MASTER/HOTEL_TRANSACCIONES_MASTER.xlsx
@@ -2762,7 +2762,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-11T19:19:17+00:00. Normalization version: v1.0.</t>
+          <t>Built 2026-05-11T19:54:43+00:00. Normalization version: v1.0.</t>
         </is>
       </c>
     </row>
